--- a/human_resources_forms/027_employee_screening_checklist--human_resources_forms.xlsx
+++ b/human_resources_forms/027_employee_screening_checklist--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'label':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'label': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1003,_'label':_'individual_contributor'}</t>
+          <t>individual_contributor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'label': 'Individual Contributor'}</t>
+          <t>Individual Contributor</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2001,_'label':_'software_development'}</t>
+          <t>software_development</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2001, 'label': 'Software Development'}</t>
+          <t>Software Development</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2002,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2002, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2003,_'label':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2003, 'label': 'Customer Service'}</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3001,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3001, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3002,_'label':_'on_leave'}</t>
+          <t>on_leave</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3002, 'label': 'On Leave'}</t>
+          <t>On Leave</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3003,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3003, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4001,_'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4001, 'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4002,_'label':_'due_today'}</t>
+          <t>due_today</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4002, 'label': 'Due Today'}</t>
+          <t>Due Today</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4003,_'label':_'past_due'}</t>
+          <t>past_due</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4003, 'label': 'Past Due'}</t>
+          <t>Past Due</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5001,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5001, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5002,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5002, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6001,_'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6001, 'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6002,_'label':_'semi-annually'}</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6002, 'label': 'Semi-Annually'}</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_6003,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 6003, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_7001,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 7001, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_7002,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 7002, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_7003,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 7003, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
